--- a/descriptive tables/desc_cashtransfer.xlsx
+++ b/descriptive tables/desc_cashtransfer.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="4">
+  <si>
+    <t xml:space="preserve">province</t>
+  </si>
   <si>
     <t xml:space="preserve">variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">province</t>
   </si>
   <si>
     <t xml:space="preserve">mean_value</t>
@@ -309,11 +309,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.6"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -322,72 +319,85 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C2" s="1" t="n">
-        <v>15070.3480565371</v>
+        <v>15065.5543478261</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C3" s="1" t="n">
-        <v>22167.8005952381</v>
+        <v>18605.3194444444</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>16888.5954285714</v>
+        <v>14049.4562453254</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C5" s="1" t="n">
-        <v>39093.6712018141</v>
+        <v>37528.5600858369</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C6" s="1" t="n">
-        <v>17630.7804878049</v>
+        <v>15478.9090909091</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="n">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C7" s="1" t="n">
-        <v>25084</v>
+        <v>22357.3797814208</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="n">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C8" s="1" t="n">
-        <v>15400.7961165049</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="1" t="n">
-        <v>12000</v>
+        <v>15710.4379562044</v>
       </c>
     </row>
   </sheetData>
